--- a/01-Projects/에이팜건강-주간자금계획-자동화/양식/연구팀_주간지출계획.xlsx
+++ b/01-Projects/에이팜건강-주간자금계획-자동화/양식/연구팀_주간지출계획.xlsx
@@ -9128,7 +9128,7 @@
       <formula1>"계좌송금,법인카드,자동이체,미정"</formula1>
     </dataValidation>
     <dataValidation sqref="K2:K201" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택해 주세요." promptTitle="카드구분" prompt="지급방법이 법인카드일 때만 선택합니다." type="list">
-      <formula1>"우리카드,국민카드"</formula1>
+      <formula1>"국민카드,우리카드,농협카드"</formula1>
     </dataValidation>
     <dataValidation sqref="L2:L201" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택해 주세요." promptTitle="확정여부" prompt="자동으로 '확정'이 들어갑니다.&#10;아직 미정이면 '미확정'으로 바꾸세요." type="list">
       <formula1>"확정,미확정"</formula1>
